--- a/cases/Case_14bus_v4/pf_info_extendedCase_14bus_v4.xlsx
+++ b/cases/Case_14bus_v4/pf_info_extendedCase_14bus_v4.xlsx
@@ -555,10 +555,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.247190657585254</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-0.2639202398067484</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -578,10 +578,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.399999874773754</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.4777474523217971</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -601,10 +601,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>0.3999999965244347</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.1965455059782659</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -624,10 +624,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>-7.147607467006267E-08</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>-6.833162599639842E-08</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -647,10 +647,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>2.014159276864103E-08</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>4.799899942786734E-08</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -670,10 +670,10 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>0.3000000114487232</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.8275783989916199</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>8.582209831686782E-09</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2.372527596605778E-08</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -716,10 +716,10 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.3500000072279842</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.2226790873014739</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -739,10 +739,10 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>-1.108331021404396E-08</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>-5.633863234266734E-08</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -762,10 +762,10 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.2000000062324065</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1.480174378898358E-09</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.0249999921973591</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>-1.078442790625189E-08</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -808,10 +808,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.02499999956033877</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>-3.399166295658951E-09</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -831,10 +831,10 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>0.09999996135819123</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>-3.66863034950704E-08</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>0.1290590214292059</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>-1.196072235698509E-08</v>
       </c>
     </row>
     <row r="16" spans="1:7">
